--- a/tame_output/ON/bt/strategyON_20231214.xlsx
+++ b/tame_output/ON/bt/strategyON_20231214.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055423383477762</v>
+        <v>3.055423383477761</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42174,7 +42174,7 @@
         <v>45230</v>
       </c>
       <c r="B1768" t="n">
-        <v>3.059751997255681</v>
+        <v>3.05975199725568</v>
       </c>
       <c r="C1768" t="n">
         <v>3.034928653249013</v>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.068246518571591</v>
+        <v>3.06824651857159</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42243,7 +42243,7 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
@@ -42266,7 +42266,7 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
@@ -42289,7 +42289,7 @@
         <v>45235</v>
       </c>
       <c r="B1773" t="n">
-        <v>3.073923642968025</v>
+        <v>3.073923642968024</v>
       </c>
       <c r="C1773" t="n">
         <v>3.057781629850306</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066014</v>
+        <v>3.074518669066013</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293023</v>
+        <v>3.087505451293022</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239776</v>
+        <v>3.125945945239775</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42381,7 +42381,7 @@
         <v>45239</v>
       </c>
       <c r="B1777" t="n">
-        <v>3.12829875500301</v>
+        <v>3.128298755003009</v>
       </c>
       <c r="C1777" t="n">
         <v>3.084316661211631</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167863</v>
+        <v>3.135555340167862</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216944</v>
+        <v>3.134141625216943</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.13201899645404</v>
+        <v>3.132018996454039</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780869</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537932</v>
+        <v>3.095206606537931</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42588,7 +42588,7 @@
         <v>45248</v>
       </c>
       <c r="B1786" t="n">
-        <v>3.123416866373821</v>
+        <v>3.12341686637382</v>
       </c>
       <c r="C1786" t="n">
         <v>3.090962466394117</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502549</v>
+        <v>3.141819250502548</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728032</v>
+        <v>3.146730118728031</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702056</v>
+        <v>3.120735995702055</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823382</v>
+        <v>3.146265744823381</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524823</v>
+        <v>3.157777201524822</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068703</v>
+        <v>3.157294380068702</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714845</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083878</v>
+        <v>3.136752015083877</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666735</v>
+        <v>3.162269743666734</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.1634320910971</v>
+        <v>3.163432091097099</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.16927921276226</v>
+        <v>3.169279212762259</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.5486850020144414</v>
+        <v>0.5488542147964809</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.351715519320749</v>
+        <v>3.351783204433564</v>
       </c>
       <c r="F1811" t="n">
         <v>1.716734910009039</v>

--- a/tame_output/ON/bt/strategyON_20231214.xlsx
+++ b/tame_output/ON/bt/strategyON_20231214.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.2%</t>
         </is>
       </c>
     </row>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.5488542147964809</v>
+        <v>0.5491078717256928</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.351783204433564</v>
+        <v>3.351884667205249</v>
       </c>
       <c r="F1811" t="n">
         <v>1.716734910009039</v>

--- a/tame_output/ON/bt/strategyON_20231214.xlsx
+++ b/tame_output/ON/bt/strategyON_20231214.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>407.4%</t>
+          <t>427.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-87.5%</t>
+          <t>-103.9%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,27 +1145,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-13.8%</t>
         </is>
       </c>
     </row>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.5491078717256928</v>
+        <v>0.3852012919119258</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.351884667205249</v>
+        <v>3.286322035279742</v>
       </c>
       <c r="F1811" t="n">
         <v>1.716734910009039</v>
